--- a/testdata/testeksempel-02-fasit.xlsx
+++ b/testdata/testeksempel-02-fasit.xlsx
@@ -713,10 +713,10 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="3" t="inlineStr"/>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Status: beregnet med skript, ikke kontrollert for hånd ennå.</t>
+          <t>Status: Kontrollert for hånd av Carmen 2026-10-24 (testeksempel 02, alle 8 deler, tall og eksepsjoner, se testdata/kontroll/). Testeksempel 01 samsvarer med fasiten fra 2026-10-19.</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Status: beregnet med skript, ikke kontrollert for hånd ennå.</t>
+          <t>Status: Kontrollert for hånd av Carmen 2026-10-24 (testeksempel 02, alle 8 deler, tall og eksepsjoner, se testdata/kontroll/). Testeksempel 01 samsvarer med fasiten fra 2026-10-19.</t>
         </is>
       </c>
     </row>
